--- a/automation/reports/Excel/Summary_Report.xlsx
+++ b/automation/reports/Excel/Summary_Report.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05T19:17:15</t>
+          <t>2026-10-05T21:12:25</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>450 (95.74%)</t>
+          <t>447 (95.11%)</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2095.26</v>
+        <v>2083.59</v>
       </c>
     </row>
     <row r="11">
